--- a/reports/t1_methods_form_v0.xlsx
+++ b/reports/t1_methods_form_v0.xlsx
@@ -542,7 +542,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MVASageBio</t>
+          <t>JiuTian Bio</t>
         </is>
       </c>
     </row>
